--- a/mosip_master/xlsx/ui_spec.xlsx
+++ b/mosip_master/xlsx/ui_spec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DC8D75-684A-4465-8799-4D8032B03E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04C5009-E5DA-4645-B9D9-41C0591431D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -488,1539 +488,6 @@
 		]
 	}
 ]</t>
-  </si>
-  <si>
-    <t>[
-	{
-		"id": "IDSchemaVersion",
-		"inputRequired": false,
-		"type": "number",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "ID Schema Version",
-		"label": {
-			"por": "IDSchemaVersion",
-			"eng": "IDSchemaVersion"
-		},
-		"controlType": null,
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "none",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": null,
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "IdSchemaVersion"
-	},
-	{
-		"id": "UIN",
-		"inputRequired": false,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "UIN",
-		"label": {
-			"por": "UIN",
-			"eng": "UIN"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "none",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": null,
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "UIN"
-	},
-	{
-		"id": "firstName",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "First Name",
-		"label": {
-			"por": "Primeiro nome",
-			"eng": "First Name"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^(?=.{2,50}$).*",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "FullName",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "firstName"
-	},
-	{
-		"id": "surname",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Surname",
-		"label": {
-			"por": "Sobrenome",
-			"eng": "Surname"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^(?=.{2,50}$).*",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "FullName",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "surname"
-	},
-	{
-		"id": "dateOfBirth",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "dateOfBirth",
-		"label": {
-			"por": "Data de nascimento",
-			"eng": "Date of Birth"
-		},
-		"controlType": "ageDate",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "DateOfBirth",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "dateOfBirth"
-	},
-	{
-		"id": "gender",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "gender",
-		"label": {
-			"por": "Gênero",
-			"eng": "Gender"
-		},
-		"controlType": "button",
-		"fieldType": "dynamic",
-		"format": "",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": "group1",
-		"visible": null,
-		"contactType": null,
-		"group": "Gender",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "gender"
-	},
-	{
-		"id": "height",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Height",
-		"label": {
-			"por": "Altura (cm)",
-			"eng": "Height (cm)"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^[0-9]{1,3}$",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "PhysicalDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "height"
-	},
-	{
-		"id": "residenceStatus",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "residenceStatus",
-		"label": {
-			"por": "Status de residência",
-			"eng": "Residence Status"
-		},
-		"controlType": "dropdown",
-		"fieldType": "dynamic",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "kyc",
-		"alignmentGroup": "group1",
-		"visible": null,
-		"contactType": null,
-		"group": "ResidenceStatus",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "residenceStatus"
-	},
-	{
-		"id": "countryOfCitizenship",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Country of Citizenship",
-		"label": {
-			"por": "País de cidadania",
-			"eng": "Country of Citizenship"
-		},
-		"controlType": "dropdown",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "CountryOfCitizenship",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "countryOfCitizenship"
-	},
-	{
-		"id": "maritalStatus",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Marital Status",
-		"label": {
-			"por": "Estado civil",
-			"eng": "Marital Status"
-		},
-		"controlType": "dropdown",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "MaritalStatus",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "maritalStatus"
-	},
-	{
-		"id": "fatherName",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Father's Name",
-		"label": {
-			"por": "Nome do pai",
-			"eng": "Father's Name"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^(?=.{2,50}$).*",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "ParentsDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "fatherName"
-	},
-	{
-		"id": "motherName",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Mother's Name",
-		"label": {
-			"por": "Nome da mãe",
-			"eng": "Mother's Name"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^(?=.{2,50}$).*",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "ParentsDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "motherName"
-	},
-	{
-		"id": "addressLine1",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "addressLine1",
-		"label": {
-			"por": "Endereço, linha 1",
-			"eng": "Address Line 1"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^(?=.{0,50}$).*",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": "address",
-		"visible": null,
-		"contactType": "Postal",
-		"group": "Address",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "addressLine1"
-	},
-	{
-		"id": "addressLine2",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "addressLine2",
-		"label": {
-			"por": "Endereço, linha 2",
-			"eng": "Address Line 2"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^(?=.{3,50}$).*",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": "address",
-		"visible": null,
-		"contactType": "Postal",
-		"group": "Address",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "addressLine2"
-	},
-	{
-		"id": "island",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Island",
-		"label": {
-			"por": "Ilha",
-			"eng": "Island"
-		},
-		"controlType": "dropdown",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": "LocationLocal",
-		"visible": null,
-		"contactType": "Postal",
-		"group": "LocationLocal",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "Ilhas"
-	},
-	{
-		"id": "district",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "District",
-		"label": {
-			"por": "Distrito",
-			"eng": "District"
-		},
-		"controlType": "dropdown",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": "LocationLocal",
-		"visible": null,
-		"contactType": "Postal",
-		"group": "LocationLocal",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "Distrito"
-	},
-	{
-		"id": "town",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Town",
-		"label": {
-			"por": "Cidade",
-			"eng": "Town"
-		},
-		"controlType": "dropdown",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": "LocationLocal",
-		"visible": null,
-		"contactType": "Postal",
-		"group": "LocationLocal",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "Cidade"
-	},
-	{
-		"id": "municipality",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Municipality",
-		"label": {
-			"por": "Município",
-			"eng": "Municipality"
-		},
-		"controlType": "dropdown",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": "LocationLocal",
-		"visible": null,
-		"contactType": "Postal",
-		"group": "LocationLocal",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "Município"
-	},
-	{
-		"id": "mobileNumber",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Mobile Number",
-		"label": {
-			"por": "Número de celular",
-			"eng": "Mobile Number"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^\\+239\\s?[0-9]{7}$",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": "contact",
-		"visible": null,
-		"contactType": "Phone",
-		"group": "Phone",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "MobileNumber"
-	},
-	{
-		"id": "email",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "email",
-		"label": {
-			"por": "E-mail",
-			"eng": "Email"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "pvt",
-		"alignmentGroup": "contact",
-		"visible": null,
-		"contactType": "email",
-		"group": "Email",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "Email"
-	},
-	{
-		"id": "introducerName",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "introducerName",
-		"label": {
-			"por": "Nome do responsável legal",
-			"eng": "Legal Guardian Name"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "evidence",
-		"alignmentGroup": "introducer",
-		"visible": {
-			"engine": "MVEL",
-			"expr": "identity.get('ageGroup') == 'INFANT'"
-		},
-		"contactType": null,
-		"group": "IntroducerDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "identity.get('ageGroup') == 'INFANT'"
-			}
-		],
-		"subType": "introducerName"
-	},
-	{
-		"id": "introducerRID",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "introducerRID",
-		"label": {
-			"por": "RID do responsável legal",
-			"eng": "Legal Guardian RID"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^([0-9]{10,30})$",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "evidence",
-		"alignmentGroup": "introducer",
-		"visible": {
-			"engine": "MVEL",
-			"expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"
-		},
-		"contactType": null,
-		"group": "IntroducerDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"
-			}
-		],
-		"subType": "RID"
-	},
-	{
-		"id": "introducerUIN",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "introducerUIN",
-		"label": {
-			"por": "UIN do responsável legal",
-			"eng": "Legal Guardian UIN"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^([0-9]{10,30})$",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "evidence",
-		"alignmentGroup": "introducer",
-		"visible": {
-			"engine": "MVEL",
-			"expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"
-		},
-		"contactType": null,
-		"group": "IntroducerDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"
-			}
-		],
-		"subType": "UIN"
-	},
-	{
-		"id": "passportNumber",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Passport Number",
-		"label": {
-			"por": "Número do passaporte",
-			"eng": "Passport Number"
-		},
-		"controlType": "textbox",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "kyc",
-		"alignmentGroup": null,
-		"visible": {
-			"engine": "MVEL",
-			"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-		},
-		"contactType": null,
-		"group": "PassportDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-			}
-		],
-		"subType": "passportNumber"
-	},
-	{
-		"id": "passportIssuingCountry",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Passport Issuing Country",
-		"label": {
-			"por": "País emissor",
-			"eng": "Issuing Country"
-		},
-		"controlType": "dropdown",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "kyc",
-		"alignmentGroup": null,
-		"visible": {
-			"engine": "MVEL",
-			"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-		},
-		"contactType": null,
-		"group": "PassportDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-			}
-		],
-		"subType": "passportIssuingCountry"
-	},
-	{
-		"id": "passportDateOfIssue",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Date of Issue",
-		"label": {
-			"por": "Data de emissão",
-			"eng": "Date of Issue"
-		},
-		"controlType": "ageDate",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "kyc",
-		"alignmentGroup": "PassportDetails",
-		"visible": {
-			"engine": "MVEL",
-			"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-		},
-		"contactType": null,
-		"group": "PassportDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-			}
-		],
-		"subType": "passportDateOfIssue"
-	},
-	{
-		"id": "passportDateOfExpiry",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Date of Expiry",
-		"label": {
-			"por": "Data de validade",
-			"eng": "Date of Expiry"
-		},
-		"controlType": "ageDate",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [
-			{
-				"type": "regex",
-				"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-				"arguments": [],
-				"langCode": null,
-				"errorCode": null
-			}
-		],
-		"fieldCategory": "kyc",
-		"alignmentGroup": "PassportDetails",
-		"visible": {
-			"engine": "MVEL",
-			"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-		},
-		"contactType": null,
-		"group": "PassportDetails",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-			}
-		],
-		"subType": "passportDateOfExpiry"
-	},
-	{
-		"id": "proofOfAddress",
-		"inputRequired": true,
-		"type": "documentType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "proofOfAddress",
-		"label": {
-			"por": "Comprovante de endereço",
-			"eng": "Address Proof"
-		},
-		"controlType": "fileupload",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "Documents",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"conditionalBioAttributes": null,
-		"exceptionPhotoRequired": false,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "identity.isNew || ( identity.isUpdate &amp;&amp; (identity.updatableFields contains 'addressLine1' || identity.updatableFields contains 'addressLine2' || identity.updatableFields contains 'addressLine3'))"
-			}
-		],
-		"subType": "POA"
-	},
-	{
-		"id": "proofOfIdentity",
-		"inputRequired": true,
-		"type": "documentType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "proofOfIdentity",
-		"label": {
-			"por": "Prova de identidade",
-			"eng": "Identity Proof"
-		},
-		"controlType": "fileupload",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "Documents",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "identity.isNew || ( identity.isUpdate &amp;&amp; identity.updatableFields contains 'fullName')"
-			}
-		],
-		"subType": "POI"
-	},
-	{
-		"id": "proofOfRelationship",
-		"inputRequired": true,
-		"type": "documentType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "proofOfRelationship",
-		"label": {
-			"por": "Prova de relacionamento",
-			"eng": "Relationship Proof"
-		},
-		"controlType": "fileupload",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "Documents",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "( identity.isNew &amp;&amp; identity.isChild ) || ( identity.isUpdate &amp;&amp; (identity.updatableFieldGroups contains 'IntroducerDetails' || identity.isChild))"
-			}
-		],
-		"subType": "POR"
-	},
-	{
-		"id": "proofOfDateOfBirth",
-		"inputRequired": true,
-		"type": "documentType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "proofOfDateOfBirth",
-		"label": {
-			"por": "Prova de data de nascimento",
-			"eng": "DOB Proof"
-		},
-		"controlType": "fileupload",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "Documents",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "identity.isUpdate &amp;&amp; identity.updatableFields contains 'dateOfBirth'"
-			}
-		],
-		"subType": "POB"
-	},
-	{
-		"id": "proofOfException",
-		"inputRequired": true,
-		"type": "documentType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "proofOfException",
-		"label": {
-			"por": "Prova de exceção",
-			"eng": "Exception Proof"
-		},
-		"controlType": "fileupload",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "evidence",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "Documents",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": false,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "POE"
-	},
-	{
-		"id": "individualBiometrics",
-		"inputRequired": true,
-		"type": "biometricsType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "",
-		"label": {
-			"por": "Biometria do Candidato",
-			"eng": "Applicant Biometrics"
-		},
-		"controlType": "biometrics",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "Biometrics",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": true,
-		"bioAttributes": [
-			"leftEye",
-			"rightEye",
-			"rightIndex",
-			"rightLittle",
-			"rightRing",
-			"rightMiddle",
-			"leftIndex",
-			"leftLittle",
-			"leftRing",
-			"leftMiddle",
-			"leftThumb",
-			"rightThumb",
-			"face"
-		],
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "(identity.isNew || identity.isLost || ( identity.isUpdate &amp;&amp; identity.updatableFieldGroups contains 'Biometrics'))"
-			}
-		],
-		"subType": "applicant"
-	},
-	{
-		"id": "individualAuthBiometrics",
-		"inputRequired": true,
-		"type": "biometricsType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Usado para armazenar dados biométricos apenas para autenticação",
-		"label": {
-			"por": "Biometria de autenticação",
-			"eng": "Authentication Biometrics"
-		},
-		"controlType": "biometrics",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": null,
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": false,
-		"bioAttributes": [
-			"leftEye",
-			"rightEye",
-			"rightIndex",
-			"rightLittle",
-			"rightRing",
-			"rightMiddle",
-			"leftIndex",
-			"leftLittle",
-			"leftRing",
-			"leftMiddle",
-			"leftThumb",
-			"rightThumb",
-			"face"
-		],
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "!identity.isChild &amp;&amp; identity.isUpdate &amp;&amp; !(identity.updatableFieldGroups contains 'Biometrics' || identity.updatableFieldGroups contains 'IntroducerDetails')"
-			}
-		],
-		"subType": "applicant-auth"
-	},
-	{
-		"id": "introducerBiometrics",
-		"inputRequired": true,
-		"type": "biometricsType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "",
-		"label": {
-			"por": "Biometria do Introdutor",
-			"eng": "Introducer Biometrics"
-		},
-		"controlType": "biometrics",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "pvt",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "Biometrics",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": null,
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": false,
-		"bioAttributes": [
-			"leftEye",
-			"rightEye",
-			"rightIndex",
-			"rightLittle",
-			"rightRing",
-			"rightMiddle",
-			"leftIndex",
-			"leftLittle",
-			"leftRing",
-			"leftMiddle",
-			"leftThumb",
-			"rightThumb",
-			"face"
-		],
-		"requiredOn": [
-			{
-				"engine": "MVEL",
-				"expr": "(identity.isChild &amp;&amp; identity.isNew) || (identity.isUpdate &amp;&amp; identity.updatableFieldGroups contains 'IntroducerDetails') || !(identity.get('introducerName') == nil || identity.get('introducerName') == empty)"
-			}
-		],
-		"subType": "introducer"
-	},
-	{
-		"id": "consentText",
-		"inputRequired": true,
-		"type": "simpleType",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "Consent",
-		"label": {},
-		"controlType": "html",
-		"fieldType": "default",
-		"format": "none",
-		"validators": [],
-		"fieldCategory": "evidence",
-		"alignmentGroup": null,
-		"visible": null,
-		"contactType": null,
-		"group": "consentText",
-		"groupLabel": null,
-		"changeAction": null,
-		"transliterate": false,
-		"templateName": "Registration Consent",
-		"fieldLayout": null,
-		"locationHierarchy": null,
-		"required": true,
-		"bioAttributes": null,
-		"requiredOn": [],
-		"subType": "consentText"
-	},
-	{
-		"id": "consent",
-		"inputRequired": true,
-		"type": "string",
-		"minimum": 0,
-		"maximum": 0,
-		"description": "consent accepted",
-		"label": {
-			"por": "Li e aceito os termos e condições para compartilhar minhas informações de identificação pessoal (PII)",
-			"eng": "I have read and accept terms and condi</t>
-  </si>
-  <si>
-    <t>[
-	{
-		"order": 1,
-		"name": "ConsentDetails",
-		"label": {
-			"por": "Consentimento",
-			"eng": "Consent"
-		},
-		"caption": {
-			"por": "Consentimento",
-			"eng": "Consent"
-		},
-		"fields": [
-			"consentText",
-			"consent"
-		],
-		"layoutTemplate": null,
-		"preRegFetchRequired": false,
-		"active": false
-	},
-	{
-		"order": 2,
-		"name": "DemographicDetails",
-		"label": {
-			"por": "Detalhes demográficos",
-			"eng": "Demographic Details"
-		},
-		"caption": {
-			"por": "Detalhes demográficos",
-			"eng": "Demographic Details"
-		},
-		"fields": [
-			"firstName",
-			"surName",
-			"dateOfBirth",
-			"gender",
-			"height",
-			"countryOfCitizenship",
-			"maritalStatus",
-			"fatherName",
-			"motherName",
-			"addressLine1",
-			"addressLine2",
-			"residenceStatus",
-			"island",
-			"district",
-			"city",
-			"municipality",
-			"mobileNumber",
-			"email",
-			"introducerName",
-			"introducerRID",
-			"introducerUIN",
-			"passportNumber",
-			"passportIssuingCountry",
-			"passportDateOfIssue",
-			"passportDateOfExpiry"
-		],
-		"layoutTemplate": null,
-		"preRegFetchRequired": true,
-		"active": false
-	},
-	{
-		"order": 3,
-		"name": "DocumentsDetails",
-		"label": {
-			"por": "Carregamento de documentos",
-			"eng": "Document upload"
-		},
-		"caption": {
-			"por": "Documentos",
-			"eng": "Documents"
-		},
-		"fields": [
-			"proofOfAddress",
-			"proofOfIdentity",
-			"proofOfRelationship",
-			"proofOfDateOfBirth",
-			"proofOfException"
-		],
-		"layoutTemplate": null,
-		"preRegFetchRequired": false,
-		"active": false
-	},
-	{
-		"order": 4,
-		"name": "BiometricDetails",
-		"label": {
-			"por": "Detalhes biométricos",
-			"eng": "Biometric Details"
-		},
-		"caption": {
-			"por": "Detalhes biométricos",
-			"eng": "Biometric Details"
-		},
-		"fields": [
-			"individualBiometrics",
-			"individualAuthBiometrics",
-			"introducerBiometrics"
-		],
-		"layoutTemplate": null,
-		"preRegFetchRequired": false,
-		"active": false
-	}
-]</t>
-  </si>
-  <si>
-    <t>{"id":"NEW","order":1,"flow":"NEW","label":{"por":"Novo registro","eng":"New Registration"},"screens":[{"order":1,"name":"consentdet","label":{"por":"Consentimento","eng":"Consent"},"caption":{"por":"Consentimento","eng":"Consent"},"fields":[{"id":"IDSchemaVersion","inputRequired":false,"type":"number","minimum":0,"maximum":0,"description":"ID Schema Version","label":{"eng":"IDSchemaVersion"},"controlType":null,"fieldType":"default","format":"none","validators":[],"fieldCategory":"none","alignmentGroup":null,"visible":null,"contactType":null,"group":null,"groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"IdSchemaVersion"},{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"por":"Li e aceito os termos e condições para compartilhar minhas informações pessoais.","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"por":"Idioma de notificação","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"por":"Detalhes demográficos","eng":"Demographic Details"},"caption":{"por":"Detalhes demográficos","eng":"Demographic Details"},"fields":[{"id":"firstName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"First Name","label":{"por":"Primeiro nome","eng":"First Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"firstName"},{"id":"surname","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Surname","label":{"por":"Sobrenome","eng":"Surname"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"surname"},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"por":"Data de nascimento","eng":"Date of Birth"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth"},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"por":"Gênero","eng":"Gender"},"controlType":"button","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"Gender","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"gender"},{"id":"height","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Height","label":{"por":"Altura (cm)","eng":"Height (cm)"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[0-9]{1,3}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"PhysicalDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"height"},{"id":"residenceStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"residenceStatus","label":{"por":"Status de residência","eng":"Residence Status"},"controlType":"dropdown","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"group1","visible":null,"contactType":null,"group":"ResidenceStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"residenceStatus"},{"id":"countryOfCitizenship","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Country of Citizenship","label":{"por":"País de cidadania","eng":"Country of Citizenship"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"CountryOfCitizenship","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"countryOfCitizenship"},{"id":"maritalStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Marital Status","label":{"por":"Estado civil","eng":"Marital Status"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"MaritalStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"maritalStatus"},{"id":"fatherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Father's Name","label":{"por":"Nome do pai","eng":"Father's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"fatherName"},{"id":"motherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Mother's Name","label":{"por":"Nome da mãe","eng":"Mother's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"motherName"},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"por":"Endereço, linha 1","eng":"Address Line 1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1"},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"por":"Endereço, linha 2","eng":"Address Line 2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2"},{"id":"island","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Island","label":{"por":"Ilha","eng":"Island"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Ilhas"},{"id":"district","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"District","label":{"por":"Distrito","eng":"District"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Distrito"},{"id":"town","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Town","label":{"por":"Cidade","eng":"Town"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Cidade"},{"id":"municipality","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Municipality","label":{"por":"Município","eng":"Municipality"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Município"},{"id":"mobileNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Mobile Number","label":{"por":"Número de celular","eng":"Mobile Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^\\+239\\s?[0-9]{7}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"Phone","group":"Phone","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"MobileNumber"},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"por":"E-mail","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Email","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Email"},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"introducerName","label":{"por":"Nome do responsável legal","eng":"Legal Guardian Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducerName"},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerRID","label":{"por":"RID do responsável legal","eng":"Legal Guardian RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"}],"subType":"RID"},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerUIN","label":{"por":"UIN do responsável legal","eng":"Legal Guardian UIN"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"}],"subType":"UIN"},{"id":"passportNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Passport Number","label":{"por":"Número do passaporte","eng":"Passport Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportNumber"},{"id":"passportIssuingCountry","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Passport Issuing Country","label":{"por":"País emissor","eng":"Issuing Country"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportIssuingCountry"},{"id":"passportDateOfIssue","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Issue","label":{"por":"Data de emissão","eng":"Date of Issue"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":"PassportDetails","visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportDateOfIssue"},{"id":"passportDateOfExpiry","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Expiry","label":{"por":"Data de validade","eng":"Date of Expiry"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":"PassportDetails","visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportDateOfExpiry"}],"layoutTemplate":null,"preRegFetchRequired":true,"additionalInfoRequestIdRequired":false,"active":false},{"order":3,"name":"Documents","label":{"ara":"تحميل الوثيقة","por":"Carregamento de documentos","fra":"Des documents","eng":"Document Upload"},"caption":{"por":"Documentos","eng":"Documents"},"fields":[{"id":"proofOfAddress","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfAddress","label":{"por":"Comprovante de endereço","eng":"Address Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POA"},{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"por":"Prova de identidade","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"por":"Prova de relacionamento","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"por":"Prova de data de nascimento","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POB"},{"id":"proofOfException","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"por":"Prova de exceção","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"por":"Detalhes biométricos","eng":"Biometric Details"},"caption":{"por":"Detalhes biométricos","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria do candidato","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"exceptionPhotoRequired":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[],"subType":"applicant"},{"id":"introducerBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria do Introdutor","eng":"Introducer Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"]}],"required":false,"exceptionPhotoRequired":false,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducer"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false}],"caption":{"por":"Novo registro","eng":"New Registration"},"icon":"NewReg.png","autoSelectedGroups":null,"active":true,"isActive":true}</t>
   </si>
   <si>
     <t xml:space="preserve">{
@@ -4415,6 +2882,1514 @@
 	"autoSelectedGroups": null
 }</t>
   </si>
+  <si>
+    <t>[
+	{
+		"id": "IDSchemaVersion",
+		"inputRequired": false,
+		"type": "number",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "ID Schema Version",
+		"label": {
+			"por": "IDSchemaVersion",
+			"eng": "IDSchemaVersion"
+		},
+		"controlType": null,
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "none",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": null,
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "IdSchemaVersion"
+	},
+	{
+		"id": "UIN",
+		"inputRequired": false,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "UIN",
+		"label": {
+			"por": "UIN",
+			"eng": "UIN"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "none",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": null,
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "UIN"
+	},
+	{
+		"id": "firstName",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "First Name",
+		"label": {
+			"por": "Primeiro nome",
+			"eng": "First Name"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^(?=.{2,50}$).*",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "FullName",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "firstName"
+	},
+	{
+		"id": "surname",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Surname",
+		"label": {
+			"por": "Sobrenome",
+			"eng": "Surname"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^(?=.{2,50}$).*",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "FullName",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "surname"
+	},
+	{
+		"id": "dateOfBirth",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "dateOfBirth",
+		"label": {
+			"por": "Data de nascimento",
+			"eng": "Date of Birth"
+		},
+		"controlType": "ageDate",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "DateOfBirth",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "dateOfBirth"
+	},
+	{
+		"id": "gender",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "gender",
+		"label": {
+			"por": "Gênero",
+			"eng": "Gender"
+		},
+		"controlType": "button",
+		"fieldType": "dynamic",
+		"format": "",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": "group1",
+		"visible": null,
+		"contactType": null,
+		"group": "Gender",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "gender"
+	},
+	{
+		"id": "height",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Height",
+		"label": {
+			"por": "Altura (cm)",
+			"eng": "Height (cm)"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^[0-9]{1,3}$",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "PhysicalDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "height"
+	},
+	{
+		"id": "residenceStatus",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "residenceStatus",
+		"label": {
+			"por": "Status de residência",
+			"eng": "Residence Status"
+		},
+		"controlType": "dropdown",
+		"fieldType": "dynamic",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "kyc",
+		"alignmentGroup": "group1",
+		"visible": null,
+		"contactType": null,
+		"group": "ResidenceStatus",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "residenceStatus"
+	},
+	{
+		"id": "countryOfCitizenship",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Country of Citizenship",
+		"label": {
+			"por": "País de cidadania",
+			"eng": "Country of Citizenship"
+		},
+		"controlType": "dropdown",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "CountryOfCitizenship",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "countryOfCitizenship"
+	},
+	{
+		"id": "maritalStatus",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Marital Status",
+		"label": {
+			"por": "Estado civil",
+			"eng": "Marital Status"
+		},
+		"controlType": "dropdown",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "MaritalStatus",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "maritalStatus"
+	},
+	{
+		"id": "fatherName",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Father's Name",
+		"label": {
+			"por": "Nome do pai",
+			"eng": "Father's Name"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^(?=.{2,50}$).*",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "ParentsDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "fatherName"
+	},
+	{
+		"id": "motherName",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Mother's Name",
+		"label": {
+			"por": "Nome da mãe",
+			"eng": "Mother's Name"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^(?=.{2,50}$).*",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "ParentsDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "motherName"
+	},
+	{
+		"id": "addressLine1",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "addressLine1",
+		"label": {
+			"por": "Endereço, linha 1",
+			"eng": "Address Line 1"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^(?=.{0,50}$).*",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": "address",
+		"visible": null,
+		"contactType": "Postal",
+		"group": "Address",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "addressLine1"
+	},
+	{
+		"id": "addressLine2",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "addressLine2",
+		"label": {
+			"por": "Endereço, linha 2",
+			"eng": "Address Line 2"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^(?=.{3,50}$).*",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": "address",
+		"visible": null,
+		"contactType": "Postal",
+		"group": "Address",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "addressLine2"
+	},
+	{
+		"id": "island",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Island",
+		"label": {
+			"por": "Ilha",
+			"eng": "Island"
+		},
+		"controlType": "dropdown",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": "LocationLocal",
+		"visible": null,
+		"contactType": "Postal",
+		"group": "LocationLocal",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "Ilhas"
+	},
+	{
+		"id": "district",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "District",
+		"label": {
+			"por": "Distrito",
+			"eng": "District"
+		},
+		"controlType": "dropdown",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": "LocationLocal",
+		"visible": null,
+		"contactType": "Postal",
+		"group": "LocationLocal",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "Distrito"
+	},
+	{
+		"id": "town",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Town",
+		"label": {
+			"por": "Cidade",
+			"eng": "Town"
+		},
+		"controlType": "dropdown",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": "LocationLocal",
+		"visible": null,
+		"contactType": "Postal",
+		"group": "LocationLocal",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "Cidade"
+	},
+	{
+		"id": "municipality",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Municipality",
+		"label": {
+			"por": "Município",
+			"eng": "Municipality"
+		},
+		"controlType": "dropdown",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": "LocationLocal",
+		"visible": null,
+		"contactType": "Postal",
+		"group": "LocationLocal",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "Município"
+	},
+	{
+		"id": "mobileNumber",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Mobile Number",
+		"label": {
+			"por": "Número de celular",
+			"eng": "Mobile Number"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^\\+239\\s?[0-9]{7}$",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": "contact",
+		"visible": null,
+		"contactType": "Phone",
+		"group": "Phone",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "MobileNumber"
+	},
+	{
+		"id": "email",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "email",
+		"label": {
+			"por": "E-mail",
+			"eng": "Email"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "pvt",
+		"alignmentGroup": "contact",
+		"visible": null,
+		"contactType": "email",
+		"group": "Email",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "Email"
+	},
+	{
+		"id": "introducerName",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "introducerName",
+		"label": {
+			"por": "Nome do responsável legal",
+			"eng": "Legal Guardian Name"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "evidence",
+		"alignmentGroup": "introducer",
+		"visible": {
+			"engine": "MVEL",
+			"expr": "identity.get('ageGroup') == 'INFANT'"
+		},
+		"contactType": null,
+		"group": "IntroducerDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "identity.get('ageGroup') == 'INFANT'"
+			}
+		],
+		"subType": "introducerName"
+	},
+	{
+		"id": "introducerRID",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "introducerRID",
+		"label": {
+			"por": "RID do responsável legal",
+			"eng": "Legal Guardian RID"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^([0-9]{10,30})$",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "evidence",
+		"alignmentGroup": "introducer",
+		"visible": {
+			"engine": "MVEL",
+			"expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"
+		},
+		"contactType": null,
+		"group": "IntroducerDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"
+			}
+		],
+		"subType": "RID"
+	},
+	{
+		"id": "introducerUIN",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "introducerUIN",
+		"label": {
+			"por": "UIN do responsável legal",
+			"eng": "Legal Guardian UIN"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^([0-9]{10,30})$",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "evidence",
+		"alignmentGroup": "introducer",
+		"visible": {
+			"engine": "MVEL",
+			"expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"
+		},
+		"contactType": null,
+		"group": "IntroducerDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"
+			}
+		],
+		"subType": "UIN"
+	},
+	{
+		"id": "passportNumber",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Passport Number",
+		"label": {
+			"por": "Número do passaporte",
+			"eng": "Passport Number"
+		},
+		"controlType": "textbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "kyc",
+		"alignmentGroup": null,
+		"visible": {
+			"engine": "MVEL",
+			"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
+		},
+		"contactType": null,
+		"group": "PassportDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
+			}
+		],
+		"subType": "passportNumber"
+	},
+	{
+		"id": "passportIssuingCountry",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Passport Issuing Country",
+		"label": {
+			"por": "País emissor",
+			"eng": "Issuing Country"
+		},
+		"controlType": "dropdown",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "kyc",
+		"alignmentGroup": null,
+		"visible": {
+			"engine": "MVEL",
+			"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
+		},
+		"contactType": null,
+		"group": "PassportDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
+			}
+		],
+		"subType": "passportIssuingCountry"
+	},
+	{
+		"id": "passportDateOfIssue",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Date of Issue",
+		"label": {
+			"por": "Data de emissão",
+			"eng": "Date of Issue"
+		},
+		"controlType": "ageDate",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "kyc",
+		"alignmentGroup": "PassportDetails",
+		"visible": {
+			"engine": "MVEL",
+			"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
+		},
+		"contactType": null,
+		"group": "PassportDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
+			}
+		],
+		"subType": "passportDateOfIssue"
+	},
+	{
+		"id": "passportDateOfExpiry",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Date of Expiry",
+		"label": {
+			"por": "Data de validade",
+			"eng": "Date of Expiry"
+		},
+		"controlType": "ageDate",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [
+			{
+				"type": "regex",
+				"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
+				"arguments": [],
+				"langCode": null,
+				"errorCode": null
+			}
+		],
+		"fieldCategory": "kyc",
+		"alignmentGroup": "PassportDetails",
+		"visible": {
+			"engine": "MVEL",
+			"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
+		},
+		"contactType": null,
+		"group": "PassportDetails",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"conditionalBioAttributes": null,
+		"exceptionPhotoRequired": false,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
+			}
+		],
+		"subType": "passportDateOfExpiry"
+	},
+	{
+		"id": "proofOfIdentity",
+		"inputRequired": true,
+		"type": "documentType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "proofOfIdentity",
+		"label": {
+			"por": "Prova de identidade",
+			"eng": "Identity Proof"
+		},
+		"controlType": "fileupload",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "Documents",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "identity.isNew || ( identity.isUpdate &amp;&amp; identity.updatableFields contains 'fullName')"
+			}
+		],
+		"subType": "POI"
+	},
+	{
+		"id": "proofOfRelationship",
+		"inputRequired": true,
+		"type": "documentType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "proofOfRelationship",
+		"label": {
+			"por": "Prova de relacionamento",
+			"eng": "Relationship Proof"
+		},
+		"controlType": "fileupload",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "Documents",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "( identity.isNew &amp;&amp; identity.isChild ) || ( identity.isUpdate &amp;&amp; (identity.updatableFieldGroups contains 'IntroducerDetails' || identity.isChild))"
+			}
+		],
+		"subType": "POR"
+	},
+	{
+		"id": "proofOfDateOfBirth",
+		"inputRequired": true,
+		"type": "documentType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "proofOfDateOfBirth",
+		"label": {
+			"por": "Prova de data de nascimento",
+			"eng": "DOB Proof"
+		},
+		"controlType": "fileupload",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "Documents",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "identity.isUpdate &amp;&amp; identity.updatableFields contains 'dateOfBirth'"
+			}
+		],
+		"subType": "POB"
+	},
+	{
+		"id": "proofOfException",
+		"inputRequired": true,
+		"type": "documentType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "proofOfException",
+		"label": {
+			"por": "Prova de exceção",
+			"eng": "Exception Proof"
+		},
+		"controlType": "fileupload",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "evidence",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "Documents",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": false,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "POE"
+	},
+	{
+		"id": "individualBiometrics",
+		"inputRequired": true,
+		"type": "biometricsType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "",
+		"label": {
+			"por": "Biometria do Candidato",
+			"eng": "Applicant Biometrics"
+		},
+		"controlType": "biometrics",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "Biometrics",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": true,
+		"bioAttributes": [
+			"leftEye",
+			"rightEye",
+			"rightIndex",
+			"rightLittle",
+			"rightRing",
+			"rightMiddle",
+			"leftIndex",
+			"leftLittle",
+			"leftRing",
+			"leftMiddle",
+			"leftThumb",
+			"rightThumb",
+			"face"
+		],
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "(identity.isNew || identity.isLost || ( identity.isUpdate &amp;&amp; identity.updatableFieldGroups contains 'Biometrics'))"
+			}
+		],
+		"subType": "applicant"
+	},
+	{
+		"id": "individualAuthBiometrics",
+		"inputRequired": true,
+		"type": "biometricsType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Usado para armazenar dados biométricos apenas para autenticação",
+		"label": {
+			"por": "Biometria de autenticação",
+			"eng": "Authentication Biometrics"
+		},
+		"controlType": "biometrics",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": null,
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": false,
+		"bioAttributes": [
+			"leftEye",
+			"rightEye",
+			"rightIndex",
+			"rightLittle",
+			"rightRing",
+			"rightMiddle",
+			"leftIndex",
+			"leftLittle",
+			"leftRing",
+			"leftMiddle",
+			"leftThumb",
+			"rightThumb",
+			"face"
+		],
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "!identity.isChild &amp;&amp; identity.isUpdate &amp;&amp; !(identity.updatableFieldGroups contains 'Biometrics' || identity.updatableFieldGroups contains 'IntroducerDetails')"
+			}
+		],
+		"subType": "applicant-auth"
+	},
+	{
+		"id": "introducerBiometrics",
+		"inputRequired": true,
+		"type": "biometricsType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "",
+		"label": {
+			"por": "Biometria do Introdutor",
+			"eng": "Introducer Biometrics"
+		},
+		"controlType": "biometrics",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "pvt",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "Biometrics",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": false,
+		"bioAttributes": [
+			"leftEye",
+			"rightEye",
+			"rightIndex",
+			"rightLittle",
+			"rightRing",
+			"rightMiddle",
+			"leftIndex",
+			"leftLittle",
+			"leftRing",
+			"leftMiddle",
+			"leftThumb",
+			"rightThumb",
+			"face"
+		],
+		"requiredOn": [
+			{
+				"engine": "MVEL",
+				"expr": "(identity.isChild &amp;&amp; identity.isNew) || (identity.isUpdate &amp;&amp; identity.updatableFieldGroups contains 'IntroducerDetails') || !(identity.get('introducerName') == nil || identity.get('introducerName') == empty)"
+			}
+		],
+		"subType": "introducer"
+	},
+	{
+		"id": "consentText",
+		"inputRequired": true,
+		"type": "simpleType",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "Consent",
+		"label": {},
+		"controlType": "html",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "evidence",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "consentText",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": "Registration Consent",
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "consentText"
+	},
+	{
+		"id": "consent",
+		"inputRequired": true,
+		"type": "string",
+		"minimum": 0,
+		"maximum": 0,
+		"description": "consent accepted",
+		"label": {
+			"por": "Li e aceito os termos e condições para compartilhar minhas informações de identificação pessoal (PII)",
+			"eng": "I have read and accept terms and conditions to share my PII"
+		},
+		"controlType": "checkbox",
+		"fieldType": "default",
+		"format": "none",
+		"validators": [],
+		"fieldCategory": "evidence",
+		"alignmentGroup": null,
+		"visible": null,
+		"contactType": null,
+		"group": "consent",
+		"groupLabel": null,
+		"changeAction": null,
+		"transliterate": false,
+		"templateName": null,
+		"fieldLayout": null,
+		"locationHierarchy": null,
+		"required": true,
+		"bioAttributes": null,
+		"requiredOn": [],
+		"subType": "consent"
+	}
+]</t>
+  </si>
+  <si>
+    <t>[
+	{
+		"order": 1,
+		"name": "ConsentDetails",
+		"label": {
+			"eng": "Consent"
+		},
+		"caption": {
+			"eng": "Consent"
+		},
+		"fields": [
+			"consentText",
+			"consent"
+		],
+		"layoutTemplate": null,
+		"preRegFetchRequired": false,
+		"active": false
+	},
+	{
+		"order": 2,
+		"name": "DemographicDetails",
+		"label": {
+			"por": "Detalhes demográficos"
+		},
+		"caption": {
+			"por": "Demographic Details"
+		},
+		"fields": [
+			"firstName",
+			"surname",
+			"dateOfBirth",
+			"gender",
+			"height",
+			"residenceStatus",
+			"countryOfCitizenship",
+			"maritalStatus",
+			"fatherName",
+			"motherName",
+			"addressLine1",
+			"addressLine2",
+			"island",
+			"district",
+			"town",
+			"municipality",
+			"mobileNumber",
+			"email",
+			"introducerName",
+			"introducerRID",
+			"introducerUIN",
+			"passportNumber",
+			"passportIssuingCountry",
+			"passportDateOfIssue",
+			"passportDateOfExpiry"
+		],
+		"layoutTemplate": null,
+		"preRegFetchRequired": true,
+		"active": false
+	},
+	{
+		"order": 3,
+		"name": "DocumentsDetails",
+		"label": {
+			"por": "Carregamento de documentos"
+		},
+		"caption": {
+			"por": "Documentos"
+		},
+		"fields": [
+			"proofOfIdentity",
+			"proofOfRelationship",
+			"proofOfDateOfBirth",
+			"proofOfException"
+		],
+		"layoutTemplate": null,
+		"preRegFetchRequired": false,
+		"active": false
+	},
+	{
+		"order": 4,
+		"name": "BiometricDetails",
+		"label": {
+			"por": "Detalhes biométricos"
+		},
+		"caption": {
+			"por": "Detalhes biométricos"
+		},
+		"fields": [
+			"individualBiometrics",
+			"individualAuthBiometrics",
+			"introducerBiometrics"
+		],
+		"layoutTemplate": null,
+		"preRegFetchRequired": false,
+		"active": false
+	}
+]</t>
+  </si>
+  <si>
+    <t>{"id":"NEW","order":1,"flow":"NEW","label":{"por":"Novo registro","eng":"New Registration"},"screens":[{"order":1,"name":"consentdet","label":{"por":"Consentimento","eng":"Consent"},"caption":{"por":"Consentimento","eng":"Consent"},"fields":[{"id":"IDSchemaVersion","inputRequired":false,"type":"number","minimum":0,"maximum":0,"description":"ID Schema Version","label":{"eng":"IDSchemaVersion"},"controlType":null,"fieldType":"default","format":"none","validators":[],"fieldCategory":"none","alignmentGroup":null,"visible":null,"contactType":null,"group":null,"groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"IdSchemaVersion"},{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"por":"Li e aceito os termos e condições para compartilhar minhas informações pessoais.","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"por":"Idioma de notificação","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"por":"Detalhes demográficos","eng":"Demographic Details"},"caption":{"por":"Detalhes demográficos","eng":"Demographic Details"},"fields":[{"id":"firstName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"First Name","label":{"por":"Primeiro nome","eng":"First Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"firstName"},{"id":"surname","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Surname","label":{"por":"Sobrenome","eng":"Surname"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"surname"},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"por":"Data de nascimento","eng":"Date of Birth"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth"},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"por":"Gênero","eng":"Gender"},"controlType":"button","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"Gender","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"gender"},{"id":"height","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Height","label":{"por":"Altura (cm)","eng":"Height (cm)"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[0-9]{1,3}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"PhysicalDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"height"},{"id":"residenceStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"residenceStatus","label":{"por":"Status de residência","eng":"Residence Status"},"controlType":"dropdown","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"group1","visible":null,"contactType":null,"group":"ResidenceStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"residenceStatus"},{"id":"countryOfCitizenship","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Country of Citizenship","label":{"por":"País de cidadania","eng":"Country of Citizenship"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"CountryOfCitizenship","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"countryOfCitizenship"},{"id":"maritalStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Marital Status","label":{"por":"Estado civil","eng":"Marital Status"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"MaritalStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"maritalStatus"},{"id":"fatherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Father's Name","label":{"por":"Nome do pai","eng":"Father's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"fatherName"},{"id":"motherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Mother's Name","label":{"por":"Nome da mãe","eng":"Mother's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"motherName"},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"por":"Endereço, linha 1","eng":"Address Line 1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1"},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"por":"Endereço, linha 2","eng":"Address Line 2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2"},{"id":"island","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Island","label":{"por":"Ilha","eng":"Island"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Ilhas"},{"id":"district","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"District","label":{"por":"Distrito","eng":"District"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Distrito"},{"id":"town","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Town","label":{"por":"Cidade","eng":"Town"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Cidade"},{"id":"municipality","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Municipality","label":{"por":"Município","eng":"Municipality"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Município"},{"id":"mobileNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Mobile Number","label":{"por":"Número de celular","eng":"Mobile Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^\\+239\\s?[0-9]{7}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"Phone","group":"Phone","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"MobileNumber"},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"por":"E-mail","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Email","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Email"},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"introducerName","label":{"por":"Nome do responsável legal","eng":"Legal Guardian Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducerName"},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerRID","label":{"por":"RID do responsável legal","eng":"Legal Guardian RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"}],"subType":"RID"},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerUIN","label":{"por":"UIN do responsável legal","eng":"Legal Guardian UIN"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"}],"subType":"UIN"},{"id":"passportNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Passport Number","label":{"por":"Número do passaporte","eng":"Passport Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportNumber"},{"id":"passportIssuingCountry","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Passport Issuing Country","label":{"por":"País emissor","eng":"Issuing Country"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportIssuingCountry"},{"id":"passportDateOfIssue","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Issue","label":{"por":"Data de emissão","eng":"Date of Issue"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":"PassportDetails","visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportDateOfIssue"},{"id":"passportDateOfExpiry","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Expiry","label":{"por":"Data de validade","eng":"Date of Expiry"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":"PassportDetails","visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportDateOfExpiry"}],"layoutTemplate":null,"preRegFetchRequired":true,"additionalInfoRequestIdRequired":false,"active":false},{"order":3,"name":"Documents","label":{"ara":"تحميل الوثيقة","por":"Carregamento de documentos","fra":"Des documents","eng":"Document Upload"},"caption":{"por":"Documentos","eng":"Documents"},"fields":[{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"por":"Prova de identidade","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"por":"Prova de relacionamento","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"por":"Prova de data de nascimento","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POB"},{"id":"proofOfException","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"por":"Prova de exceção","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"por":"Detalhes biométricos","eng":"Biometric Details"},"caption":{"por":"Detalhes biométricos","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria do candidato","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"exceptionPhotoRequired":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[],"subType":"applicant"},{"id":"introducerBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria do Introdutor","eng":"Introducer Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"]}],"required":false,"exceptionPhotoRequired":false,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducer"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false}],"caption":{"por":"Novo registro","eng":"New Registration"},"icon":"NewReg.png","autoSelectedGroups":null,"active":true,"isActive":true}</t>
+  </si>
 </sst>
 </file>
 
@@ -4864,7 +4839,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H3" s="6">
         <v>1001</v>
@@ -4918,7 +4893,7 @@
         <v>31</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H4" s="6">
         <v>1001</v>
@@ -5026,7 +5001,7 @@
         <v>34</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H6" s="6">
         <v>1001</v>
@@ -5088,7 +5063,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H7" s="6">
         <v>1001</v>
@@ -5150,7 +5125,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H8" s="6">
         <v>1001</v>
@@ -5212,7 +5187,7 @@
         <v>37</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H9" s="6">
         <v>1001</v>
